--- a/output/full_scan/batch_seq6_2026-06-05.xlsx
+++ b/output/full_scan/batch_seq6_2026-06-05.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>960.6506607521984</v>
+        <v>1205.650660752198</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>87.90000000000001</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>66.14835431120034</v>
+        <v>66.1483543364962</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>32.78242202592222</v>
+        <v>32.78242191306487</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.065066075219853</v>
@@ -570,11 +570,11 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.1271179820670438</v>
+        <v>0.1271179819716525</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>835</v>
+        <v>1125</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>32.6</v>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>77.87848922387511</v>
+        <v>77.87848923507885</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>30.82595117349075</v>
+        <v>30.8259510832126</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>6.598671671485758</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.474619631682371</v>
+        <v>0.4746196318254682</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6284</v>
+        <v>6409</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>827.1059356618483</v>
+        <v>971.2679618703808</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>111</v>
+        <v>928</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>60.35955185180633</v>
+        <v>75.33206930988723</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>42.6113036706324</v>
+        <v>24.48540891242768</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.710593566184836</v>
+        <v>1.626796187038072</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>-0.07235911653140011</v>
+        <v>23.39607404339501</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6259</v>
+        <v>6206</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>764.0474758537466</v>
+        <v>895.9750030948336</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>27.3</v>
+        <v>141.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>62.52725542014296</v>
+        <v>67.00643210396771</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>40.17133046157929</v>
+        <v>38.3944079341252</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.404747585374661</v>
+        <v>0.597500309483356</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.0029334006746806</v>
+        <v>-0.6758041517780233</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>6175</v>
+        <v>6281</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>763.3047237810348</v>
+        <v>891.8002358258819</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>96.59999999999999</v>
+        <v>52.1</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>64.18305091754152</v>
+        <v>56.79034574830771</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>48.69570591519256</v>
+        <v>20.20592934379</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.330472378103478</v>
+        <v>1.680023582588189</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>-0.4822242557470666</v>
+        <v>0.2937295529215937</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>6432</v>
+        <v>6451</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>今展科</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>758.9080313509853</v>
+        <v>885.2527536381544</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>67.3</v>
+        <v>666</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>67.56974670383619</v>
+        <v>63.05900562510944</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>46.72583605478184</v>
+        <v>42.60443761954106</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.8908031350985353</v>
+        <v>1.52527536381545</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.1379172243569781</v>
+        <v>9.490808389342952</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6166</v>
+        <v>6170</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>758.7180885514907</v>
+        <v>883.3806071029701</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>133</v>
+        <v>53.2</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>72.76992662716714</v>
+        <v>71.75608448359168</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>69.29240411988188</v>
+        <v>24.71704605184512</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.8718088551490748</v>
+        <v>1.338060710297004</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,31 +888,31 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>-0.902236719054951</v>
+        <v>0.327275301797269</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>6224</v>
+        <v>6259</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>757.3959929590856</v>
+        <v>879.0474758537466</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>84.2</v>
+        <v>27.3</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
@@ -923,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>57.15361609053475</v>
+        <v>62.52725544230046</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>37.29352061434452</v>
+        <v>40.17133046157929</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.7395992959085546</v>
+        <v>1.404747585374661</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>-1.066591605235409</v>
+        <v>0.0029334006365211</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6206</v>
+        <v>6414</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>755.9750030948336</v>
+        <v>878.8058804488584</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>141.5</v>
+        <v>384</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>67.00643217429112</v>
+        <v>66.8965613642945</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>38.39440786325962</v>
+        <v>37.93965234087763</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.597500309483356</v>
+        <v>0.8805880448858387</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>-0.6758041530181842</v>
+        <v>2.298140703145773</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6291</v>
+        <v>6290</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>751.5769113587919</v>
+        <v>866.7909852930978</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>606</v>
+        <v>350.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>60.15415631614081</v>
+        <v>67.07928761727851</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>38.70301963177594</v>
+        <v>28.94909679202949</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.1576911358791954</v>
+        <v>0.6790985293097864</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>0.2232300077849416</v>
+        <v>4.673221215292365</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6409</v>
+        <v>6282</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>696.0188601735138</v>
+        <v>856.8361010736505</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>928</v>
+        <v>63.8</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>75.33206923638039</v>
+        <v>58.89698324709344</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>24.48540881151103</v>
+        <v>35.19372651361115</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.601886017351375</v>
+        <v>1.683610107365052</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>23.39607404721089</v>
+        <v>0.8449978793750721</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6279</v>
+        <v>6189</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>687.1879765917867</v>
+        <v>845.0783888227974</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>120.5</v>
+        <v>54.3</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>57.01763278780489</v>
+        <v>63.36783098444305</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>26.05657229063207</v>
+        <v>30.12690142521111</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.218797659178662</v>
+        <v>2.007838882279733</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.1514271027691522</v>
+        <v>0.3350286753682443</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6282</v>
+        <v>6204</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>686.8361010736505</v>
+        <v>843.9850555358685</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>63.8</v>
+        <v>110.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>58.89698323694837</v>
+        <v>80.54314795806431</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>35.19372661242522</v>
+        <v>45.31382988887707</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.683610107365052</v>
+        <v>1.398505553586842</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.8449978792033628</v>
+        <v>1.75847547559049</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6281</v>
+        <v>6291</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>686.8002358258819</v>
+        <v>841.5769113587919</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>52.1</v>
+        <v>606</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>56.79034558511388</v>
+        <v>60.15415632130544</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>20.20592938859617</v>
+        <v>38.70301963177596</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.680023582588189</v>
+        <v>0.1576911358791954</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>0.2937295530742306</v>
+        <v>0.2232300077658067</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6451</v>
+        <v>6207</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>685.2527536381544</v>
+        <v>836.0327204355956</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>666</v>
+        <v>144.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>63.05900561854772</v>
+        <v>80.32054972256438</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>42.60443770516372</v>
+        <v>62.27573778859228</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.52527536381545</v>
+        <v>2.603272043559565</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>9.490808388770567</v>
+        <v>5.077452851878517</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6417</v>
+        <v>6284</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>680.8259641106216</v>
+        <v>827.1059356618483</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>140.5</v>
+        <v>111</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>58.61525386007354</v>
+        <v>60.35955186770742</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>30.58915327106261</v>
+        <v>42.61130369409089</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.5825964110621625</v>
+        <v>1.710593566184836</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,11 +1365,11 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-0.5879377415050033</v>
+        <v>-0.0723591163406105</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>680.3850857091752</v>
+        <v>820.3850857091752</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>57.6</v>
@@ -1400,10 +1400,10 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>60.68860439156912</v>
+        <v>60.68860439940475</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>36.2902310992895</v>
+        <v>36.29023103347129</v>
       </c>
       <c r="J18" s="2" t="n">
         <v>1.038508570917516</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>0.9711901590062002</v>
+        <v>0.9711901590615292</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6174</v>
+        <v>6485</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>678.7187758560814</v>
+        <v>776.25820851942</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>43.7</v>
+        <v>112</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,13 +1453,13 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>57.18733744311842</v>
+        <v>56.65325519407697</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>39.71670372531734</v>
+        <v>33.58614997384169</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.3718775856081384</v>
+        <v>1.125820851942004</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.6767318394834323</v>
+        <v>0.4874655218488453</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6196</v>
+        <v>6283</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>676.9363748522411</v>
+        <v>772.5045783704035</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>504</v>
+        <v>25.35</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>70.3644520845524</v>
+        <v>59.21769222789973</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>48.76082651991391</v>
+        <v>26.55242084799519</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.6936374852241091</v>
+        <v>0.7504578370403473</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.097947163996764</v>
+        <v>-0.0113621147161881</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6446</v>
+        <v>6418</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>676.6636617558872</v>
+        <v>772.4873697122949</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>937</v>
+        <v>34.25</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>70.03737511061253</v>
+        <v>62.35517717044281</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>42.73988788331174</v>
+        <v>20.2251170318117</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.6663661755887187</v>
+        <v>3.748736971229493</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>5.47663788041816</v>
+        <v>0.4369971208472348</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6227</v>
+        <v>6196</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>675.7739435972421</v>
+        <v>771.9363748522411</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>128</v>
+        <v>504</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,49 +1612,49 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>60.21462674153837</v>
+        <v>70.36445208742263</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>43.72823278656746</v>
+        <v>48.76082640455692</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.5773943597242152</v>
+        <v>0.6936374852241091</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>-0.0871568280373029</v>
+        <v>1.097947164473787</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6239</v>
+        <v>6274</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>675.7558235461414</v>
+        <v>767.7661418035797</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>338</v>
+        <v>1610</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,49 +1665,49 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>63.76668175169622</v>
+        <v>61.00144324406774</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>37.3005360446125</v>
+        <v>38.43986571817948</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5755823546141375</v>
+        <v>1.776614180357962</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>3.294017724110635</v>
+        <v>-3.575452114715745</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6435</v>
+        <v>6239</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>675.1919875848267</v>
+        <v>765.7558235461414</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>272.5</v>
+        <v>338</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>60.93811316627026</v>
+        <v>63.76668174478522</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>38.57580371396559</v>
+        <v>37.30053607877995</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.5191987584826732</v>
+        <v>0.5755823546141375</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.2697731666916745</v>
+        <v>3.294017724873783</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6189</v>
+        <v>6415</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>675.0783888227974</v>
+        <v>765.00785287111</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>54.3</v>
+        <v>582</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>63.36783083706217</v>
+        <v>59.41348769997994</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>30.12690121911801</v>
+        <v>42.48420374985204</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.007838882279733</v>
+        <v>0.5007852871110006</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.3350286751202098</v>
+        <v>-7.001584524981354</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6415</v>
+        <v>6175</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>675.00785287111</v>
+        <v>763.3047237810348</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>582</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>59.41348779264381</v>
+        <v>64.18305093136925</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>42.48420340683845</v>
+        <v>48.69570584158512</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.5007852871110006</v>
+        <v>1.330472378103478</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-7.001584532326966</v>
+        <v>-0.4822242557279903</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6411</v>
+        <v>6271</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>同欣電</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>674.8573280095833</v>
+        <v>762.5671418953923</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>99</v>
+        <v>236.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>59.48649987383792</v>
+        <v>62.82645109139204</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>36.88420262934206</v>
+        <v>41.84481251065172</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4857328009583319</v>
+        <v>0.2567141895392292</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.0418810939778291</v>
+        <v>0.5962944038442224</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6285</v>
+        <v>6279</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>674.4782113743487</v>
+        <v>762.1879765917867</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>292</v>
+        <v>120.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>55.88800365912832</v>
+        <v>57.01763329691082</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>42.41803745644177</v>
+        <v>26.05657236104685</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.4478211374348652</v>
+        <v>1.218797659178662</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-2.658120933337635</v>
+        <v>-0.1514271042001072</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6182</v>
+        <v>6432</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>合晶</t>
+          <t>今展科</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>673.8485878959916</v>
+        <v>758.9080313509853</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>85.5</v>
+        <v>67.3</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>62.92282850737163</v>
+        <v>67.5697467057413</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>55.04769304213299</v>
+        <v>46.72583599302307</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.38485878959916</v>
+        <v>0.8908031350985353</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.6240270707459619</v>
+        <v>0.1379172244619138</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6292</v>
+        <v>6166</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>673.4992169329639</v>
+        <v>758.7180885514907</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>58.00692029191165</v>
+        <v>72.7699266336831</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>40.15760343516119</v>
+        <v>69.29240414521526</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.3499216932963874</v>
+        <v>0.8718088551490748</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.008228749194602701</v>
+        <v>-0.902236718864156</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6274</v>
+        <v>6224</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>672.7661418035797</v>
+        <v>757.3959929590856</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1610</v>
+        <v>84.2</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>61.0014432396931</v>
+        <v>57.15361608680516</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>38.43986577352803</v>
+        <v>37.29352059602476</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.776614180357962</v>
+        <v>0.7395992959085546</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-3.57545211462056</v>
+        <v>-1.066591604958766</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6271</v>
+        <v>6174</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>同欣電</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>672.5671418953923</v>
+        <v>753.7187758560814</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>236.5</v>
+        <v>43.7</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>62.82645107513751</v>
+        <v>57.18733745888176</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>41.84481261940817</v>
+        <v>39.71670375229805</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.2567141895392292</v>
+        <v>0.3718775856081384</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.596294403538959</v>
+        <v>-0.6767318394452739</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6405</v>
+        <v>6197</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>672.1572870336799</v>
+        <v>753.538180172009</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>76</v>
+        <v>325</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>64.63284504640453</v>
+        <v>78.2777932691546</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>53.56348800251364</v>
+        <v>54.67563455644803</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.2157287033679923</v>
+        <v>1.353818017200899</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.1461815032427846</v>
+        <v>5.350039419203114</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6290</v>
+        <v>6269</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>661.7909852930978</v>
+        <v>716.4112343271055</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>350.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>67.07928762346729</v>
+        <v>54.59470517654231</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>28.94909691292843</v>
+        <v>25.76331830438629</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.6790985293097864</v>
+        <v>1.141123432710546</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>4.673221214643668</v>
+        <v>1.234811581865404</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6245</v>
+        <v>6208</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>661.4871831697706</v>
+        <v>708.1430635859101</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>87.2</v>
+        <v>83.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>55.14643326257622</v>
+        <v>45.03478432882054</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>33.31292646175425</v>
+        <v>36.6528873127975</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.6487183169770543</v>
+        <v>0.3143063585910086</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>-0.2822767932410444</v>
+        <v>-2.54053116615992</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6170</v>
+        <v>6173</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>653.3806071029701</v>
+        <v>707.6977714948903</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>53.2</v>
+        <v>223.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>71.75608427394772</v>
+        <v>70.86676348941862</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>24.71704600238477</v>
+        <v>53.26723639680382</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.338060710297004</v>
+        <v>0.2697771494890316</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.327275301797269</v>
+        <v>-0.7015848218337339</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6204</v>
+        <v>6164</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>643.9850555358685</v>
+        <v>704.0754440820488</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>110.5</v>
+        <v>13.1</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>80.54314795671829</v>
+        <v>58.69757434042567</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45.31382989638825</v>
+        <v>19.99236586122714</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.398505553586842</v>
+        <v>0.9075444082048724</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>1.758475475180283</v>
+        <v>0.1307497838698826</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6207</v>
+        <v>6192</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>636.0327204355956</v>
+        <v>689.4153680126728</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>144.5</v>
+        <v>129</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>80.32054972157275</v>
+        <v>53.98646438431472</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>62.27573788436858</v>
+        <v>25.51796993383488</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>2.603272043559565</v>
+        <v>0.4415368012672819</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>5.07745285151602</v>
+        <v>-0.3138312837386543</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6173</v>
+        <v>6456</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>信昌電</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>632.6977714948903</v>
+        <v>684.3856560204116</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>223.5</v>
+        <v>82.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>70.86676348514239</v>
+        <v>56.29735492839383</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>53.26723658782851</v>
+        <v>21.29501439474551</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.2697771494890316</v>
+        <v>0.9385656020411626</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.7015848219959082</v>
+        <v>1.133402569224829</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6449</v>
+        <v>6417</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>631.4356998801145</v>
+        <v>680.8259641106216</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>371</v>
+        <v>140.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>69.53990747167612</v>
+        <v>58.61525387053582</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>57.94124158801289</v>
+        <v>30.58915329100513</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.1435699880114442</v>
+        <v>0.5825964110621625</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>3.150141611207239</v>
+        <v>-0.5879377413523628</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6414</v>
+        <v>6446</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>618.8058804488584</v>
+        <v>676.6636617558872</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>384</v>
+        <v>937</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>66.8965613664826</v>
+        <v>70.037375118349</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>37.93965232468937</v>
+        <v>42.73988787413983</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.8805880448858387</v>
+        <v>0.6663661755887187</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>2.298140702573383</v>
+        <v>5.476637880895083</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6208</v>
+        <v>6227</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>618.1430635859101</v>
+        <v>675.7739435972421</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>83.5</v>
+        <v>128</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>45.03478430642436</v>
+        <v>60.21462679068834</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>36.65288734638802</v>
+        <v>43.72823269727412</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.3143063585910086</v>
+        <v>0.5773943597242152</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-2.540531166150385</v>
+        <v>-0.087156827350439</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6277</v>
+        <v>6435</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>617.2246816619599</v>
+        <v>675.1919875848267</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>77.09999999999999</v>
+        <v>272.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>57.19920683155173</v>
+        <v>60.93811317421292</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>58.24769458686403</v>
+        <v>38.57580367665336</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7224681661959941</v>
+        <v>0.5191987584826732</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.1468271415470896</v>
+        <v>0.2697731670160159</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6237</v>
+        <v>6411</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>614.1777559756687</v>
+        <v>674.8573280095833</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>49.7</v>
+        <v>99</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>53.54906648491562</v>
+        <v>59.48649989808338</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>44.42966562423878</v>
+        <v>36.88420257753519</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.4177755975668713</v>
+        <v>0.4857328009583319</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.3549114104031328</v>
+        <v>-0.041881093806122</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6485</v>
+        <v>6285</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>606.25820851942</v>
+        <v>674.4782113743487</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>112</v>
+        <v>292</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,49 +2831,49 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>56.65325513736534</v>
+        <v>55.88800372115065</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>33.58614998068939</v>
+        <v>42.4180375550952</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.125820851942004</v>
+        <v>0.4478211374348652</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.4874655224975308</v>
+        <v>-2.658120933433057</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6234</v>
+        <v>6272</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>603.6528670699519</v>
+        <v>673.9826465116854</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>47.35</v>
+        <v>37.7</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>48.07188847829749</v>
+        <v>64.03334891232305</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>28.06844975146842</v>
+        <v>42.62421099184061</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.3652867069951915</v>
+        <v>1.398264651168542</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-1.163212253160336</v>
+        <v>0.7370417653264373</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6263</v>
+        <v>6182</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>合晶</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>602.319513233038</v>
+        <v>673.8485878959916</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>166.5</v>
+        <v>85.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>48.26466542154923</v>
+        <v>62.92282850428787</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>27.78487847621429</v>
+        <v>55.04769290654245</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.7319513233038074</v>
+        <v>0.38485878959916</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-2.251890564110792</v>
+        <v>0.6240270709081486</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6257</v>
+        <v>6292</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>601.7114449306689</v>
+        <v>673.4992169329639</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>223</v>
+        <v>61</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>57.38937979457142</v>
+        <v>58.00692032552501</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>43.10149258768188</v>
+        <v>40.15760323533389</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.6711444930668899</v>
+        <v>0.3499216932963874</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-1.849116462625174</v>
+        <v>-0.008228749194602701</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6192</v>
+        <v>6405</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>599.4153680126728</v>
+        <v>672.1572870336799</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>53.98646436456534</v>
+        <v>64.63284504582271</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>25.51796993841673</v>
+        <v>53.56348802255538</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.4415368012672819</v>
+        <v>0.2157287033679923</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.3138312839485233</v>
+        <v>0.1461815033858755</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6213</v>
+        <v>6205</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>589.8597846474191</v>
+        <v>664.8389776675448</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>254.5</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>47.57425874570549</v>
+        <v>50.9662637909797</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>22.17691517203104</v>
+        <v>24.80686977685371</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.4859784647419182</v>
+        <v>0.4838977667544796</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>-2.689786314071905</v>
+        <v>0.0328429160804517</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6197</v>
+        <v>6245</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>583.538180172009</v>
+        <v>661.4871831697706</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>325</v>
+        <v>87.2</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>78.2777932654994</v>
+        <v>55.14643329888218</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>54.67563467170974</v>
+        <v>33.31292649723709</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.353818017200899</v>
+        <v>0.6487183169770543</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>5.350039418916907</v>
+        <v>-0.2822767927449621</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6418</v>
+        <v>6442</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>572.4873697122949</v>
+        <v>657.2699743492909</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>34.25</v>
+        <v>2055</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>62.3551771538986</v>
+        <v>53.44541089474356</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>20.22511703637805</v>
+        <v>15.20186745427538</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>3.748736971229493</v>
+        <v>1.22699743492909</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.4369971207995342</v>
+        <v>23.75254587203624</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, adx_trending, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6269</v>
+        <v>6226</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>光鼎</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>546.4112343271054</v>
+        <v>649.0231846347018</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>68.09999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>54.59470517071272</v>
+        <v>55.97470466690233</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>25.76331847404934</v>
+        <v>21.12807551351582</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.141123432710546</v>
+        <v>0.9023184634701796</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>1.234811581531523</v>
+        <v>0.0854061301087522</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6283</v>
+        <v>6191</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>542.5045783704035</v>
+        <v>648.8947858886927</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>25.35</v>
+        <v>100.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>59.21769211810673</v>
+        <v>56.04842081862379</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>26.55242080292249</v>
+        <v>15.7212771360235</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.7504578370403473</v>
+        <v>1.389478588869271</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0113621147257295</v>
+        <v>0.7146541638578418</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6416</v>
+        <v>6214</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>540.5973593385244</v>
+        <v>647.090209460525</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>87.40000000000001</v>
+        <v>144.5</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,16 +3361,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>48.71023413402311</v>
+        <v>63.64981378842333</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>33.18936782222414</v>
+        <v>38.03330977492331</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.559735933852435</v>
+        <v>1.209020946052504</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.4380674340737753</v>
+        <v>2.043187439841191</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6220</v>
+        <v>6465</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>540.5236106513472</v>
+        <v>646.134442765746</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>33.6</v>
+        <v>54.9</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>57.00301312928837</v>
+        <v>60.07823296664612</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>44.01002167816358</v>
+        <v>14.51655783891294</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.052361065134719</v>
+        <v>1.113444276574607</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.3502272297506864</v>
+        <v>0.613676581943982</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6190</v>
+        <v>6470</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>539.3430488336287</v>
+        <v>642.8657653658927</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>81.3</v>
+        <v>50.4</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.77351078177334</v>
+        <v>64.71656713915252</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45.17356994722336</v>
+        <v>18.72117233254408</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.4343048833628734</v>
+        <v>0.7865765365892703</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.6327835750131783</v>
+        <v>0.3656128044819727</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6223</v>
+        <v>6449</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>532.7657134296649</v>
+        <v>631.4356998801145</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>5765</v>
+        <v>371</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>52.9948324696452</v>
+        <v>69.53990748857512</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>25.38786211260903</v>
+        <v>57.94124150605264</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.7765713429664772</v>
+        <v>0.1435699880114442</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,51 +3538,51 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-73.36482253282924</v>
+        <v>3.150141611359885</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6288</v>
+        <v>6246</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>聯嘉</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>526.8310325240927</v>
+        <v>631.0601594060487</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>20.95</v>
+        <v>16.1</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>2025-08-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="G59" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>51.62028548877775</v>
+        <v>53.25126928487911</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>23.45008925381045</v>
+        <v>17.75359767446799</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.6831032524092705</v>
+        <v>1.10601594060487</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.040911958491001</v>
+        <v>0.07164441701267681</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6205</v>
+        <v>6223</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>524.8389776675448</v>
+        <v>628.6396505831977</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>82.09999999999999</v>
+        <v>5765</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,49 +3626,49 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.96626376751438</v>
+        <v>52.9948324749771</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>24.80686959745664</v>
+        <v>25.38786198496219</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.4838977667544796</v>
+        <v>0.86396505831978</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0328429158896443</v>
+        <v>-73.36482252863129</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6203</v>
+        <v>6277</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>524.1185407001001</v>
+        <v>617.2246816619599</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>71.09999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>52.81497391681716</v>
+        <v>57.19920684841879</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>24.47306676914868</v>
+        <v>58.24769474580762</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.4118540700100098</v>
+        <v>0.7224681661959941</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-0.0729212587898895</v>
+        <v>0.1468271416043278</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6194</v>
+        <v>6237</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>育富</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>521.7412175045098</v>
+        <v>614.1777559756687</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>34.25</v>
+        <v>49.7</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>57.44121666537988</v>
+        <v>53.54906652983437</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>24.95137812272635</v>
+        <v>44.42966554387905</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.1741217504509802</v>
+        <v>0.4177755975668713</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0540025291254844</v>
+        <v>-0.3549114102409492</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6456</v>
+        <v>6234</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>514.3856560204116</v>
+        <v>603.6528670699519</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>82.5</v>
+        <v>47.35</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>56.29735492057099</v>
+        <v>48.07188850459394</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>21.2950142972425</v>
+        <v>28.06844974355814</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.9385656020411626</v>
+        <v>0.3652867069951915</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>1.133402568986322</v>
+        <v>-1.163212253074474</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6419</v>
+        <v>6263</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>512.4610317596624</v>
+        <v>602.319513233038</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>140</v>
+        <v>166.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>47.32105955967006</v>
+        <v>48.26466547125178</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>20.71512553445719</v>
+        <v>27.7848788159245</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.2461031759662426</v>
+        <v>0.7319513233038074</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-2.941146242849323</v>
+        <v>-2.251890564015378</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6215</v>
+        <v>6257</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>510.3127078014613</v>
+        <v>601.7114449306689</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>118</v>
+        <v>223</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>47.17209088300815</v>
+        <v>57.38937980235911</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>22.94403351092539</v>
+        <v>43.10149242269603</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5312707801461316</v>
+        <v>0.6711444930668899</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>-2.058902043782902</v>
+        <v>-1.849116462415274</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6226</v>
+        <v>6213</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>光鼎</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>509.0231846347018</v>
+        <v>589.8597846474191</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>13.6</v>
+        <v>254.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>55.97470459945627</v>
+        <v>47.57425875061023</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>21.12807542994492</v>
+        <v>22.1769151027641</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.9023184634701796</v>
+        <v>0.4859784647419182</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.0854061300992138</v>
+        <v>-2.689786313804781</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6191</v>
+        <v>6474</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>508.8947858886927</v>
+        <v>570.3686477349218</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>100.5</v>
+        <v>38.2</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>56.04842074655182</v>
+        <v>51.76591919808613</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>15.72127714287183</v>
+        <v>23.21232858770734</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>1.389478588869271</v>
+        <v>0.5368647734921832</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.7146541636479803</v>
+        <v>-0.0574168621633014</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6272</v>
+        <v>6412</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>503.9826465116854</v>
+        <v>568.3315402844239</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>37.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>64.03334873134281</v>
+        <v>53.73893894135104</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>42.62421099826762</v>
+        <v>40.93405422062367</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.398264651168542</v>
+        <v>1.333154028442397</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.7370417656221664</v>
+        <v>-0.300750659961702</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6470</v>
+        <v>6165</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>502.8657653658927</v>
+        <v>561.2211778552187</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>50.4</v>
+        <v>49.35</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>64.71656706883871</v>
+        <v>53.29363149194787</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>18.72117222289543</v>
+        <v>21.98907069917556</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.7865765365892703</v>
+        <v>1.622117785521875</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.3656128043388711</v>
+        <v>-0.0308862054173599</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6168</v>
+        <v>6278</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>498.4556125765584</v>
+        <v>543.8930896360395</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>26.05</v>
+        <v>206.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>44.90223511720562</v>
+        <v>51.51211747194111</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>19.27086738244448</v>
+        <v>32.63834922348156</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.3455612576558354</v>
+        <v>0.3893089636039456</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-0.268146859225005</v>
+        <v>-5.811773852273472</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6412</v>
+        <v>6416</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>478.331540284424</v>
+        <v>540.5973593385244</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>97.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>53.73893903965432</v>
+        <v>48.71023409347651</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>40.93405392380566</v>
+        <v>33.18936787777877</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.333154028442397</v>
+        <v>0.559735933852435</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.3007506610873776</v>
+        <v>-0.4380674333487393</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6214</v>
+        <v>6220</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>477.090209460525</v>
+        <v>540.5236106513472</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>144.5</v>
+        <v>33.6</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>63.64981374649702</v>
+        <v>57.00301315414412</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>38.03330967394027</v>
+        <v>44.0100216659929</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>1.209020946052504</v>
+        <v>1.052361065134719</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>2.043187439554988</v>
+        <v>0.3502272298079256</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6443</v>
+        <v>6190</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>459.5955932505867</v>
+        <v>539.3430488336287</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>39.9</v>
+        <v>81.3</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>47.15524744108155</v>
+        <v>54.77351078498032</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>25.07885391713314</v>
+        <v>45.17356985515656</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.4595593250586646</v>
+        <v>0.4343048833628734</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0036627844363185</v>
+        <v>-0.6327835746125121</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6474</v>
+        <v>6261</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>455.3686477349218</v>
+        <v>528.8500038427992</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>38.2</v>
+        <v>107.5</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>51.76591905566809</v>
+        <v>47.04093384456668</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>23.21232860571725</v>
+        <v>20.40789274813066</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5368647734921832</v>
+        <v>0.3850003842799179</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,51 +4386,51 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.0574168620679043</v>
+        <v>-2.865445792368584</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6278</v>
+        <v>6288</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>聯嘉</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>453.8930896360395</v>
+        <v>526.8310325240927</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>206.5</v>
+        <v>20.95</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-08-04</t>
         </is>
       </c>
       <c r="G75" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>51.51211746957379</v>
+        <v>52.04437235222755</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>32.63834918710318</v>
+        <v>23.428420910186</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.3893089636039456</v>
+        <v>0.6831032524092705</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-5.811773852674126</v>
+        <v>0.0410727544146973</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6217</v>
+        <v>6203</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>海韻電</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>449.6564222831479</v>
+        <v>524.1185407001001</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>254</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>44.42894616155908</v>
+        <v>52.81497406523891</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20.11984106620572</v>
+        <v>24.47306682656031</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.465642228314788</v>
+        <v>0.4118540700100098</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-4.499822026795218</v>
+        <v>-0.07292125871357009</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6266</v>
+        <v>6194</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>育富</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>447.2545617194276</v>
+        <v>521.7412175045098</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>28.05</v>
+        <v>34.25</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>55.95384793130423</v>
+        <v>57.44121670976311</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>21.84613778639352</v>
+        <v>24.95137822171627</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.7254561719427558</v>
+        <v>0.1741217504509802</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.1423716543050213</v>
+        <v>0.0540025292018015</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6165</v>
+        <v>6419</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>446.2211778552187</v>
+        <v>512.4610317596624</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>49.35</v>
+        <v>140</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>53.29363157892528</v>
+        <v>47.32105959999226</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>21.98907057944945</v>
+        <v>20.71512561372557</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.622117785521875</v>
+        <v>0.2461031759662426</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.0308862059038828</v>
+        <v>-2.941146242582214</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6465</v>
+        <v>6472</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>446.1344427657461</v>
+        <v>512.2897521814568</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>54.9</v>
+        <v>371.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>60.07823292917497</v>
+        <v>47.42763408315031</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>14.51655773118529</v>
+        <v>26.42912493658667</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.113444276574607</v>
+        <v>0.7289752181456796</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.6136765820911303</v>
+        <v>2.397758301117115</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6164</v>
+        <v>6215</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>444.0754440820487</v>
+        <v>510.3127078014613</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>13.1</v>
+        <v>118</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>58.69757428816455</v>
+        <v>47.17209093810641</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19.99236582457637</v>
+        <v>22.94403348026524</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.9075444082048724</v>
+        <v>0.5312707801461316</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.1307497838221828</v>
+        <v>-2.058902043115117</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6426</v>
+        <v>6275</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>439.5259073609012</v>
+        <v>502.9579997621631</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>229.5</v>
+        <v>50.1</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>42.93948136136314</v>
+        <v>50.2796320741101</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>23.33927291911828</v>
+        <v>21.70422453228122</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.4525907360901153</v>
+        <v>0.7957999762163083</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-6.654948736596346</v>
+        <v>0.4073094427697285</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6261</v>
+        <v>6185</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>438.8500038427992</v>
+        <v>501.6321773861576</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>107.5</v>
+        <v>14.35</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>47.04093383257713</v>
+        <v>56.14113389314532</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>20.40789270866597</v>
+        <v>19.15640910488848</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.3850003842799179</v>
+        <v>0.6632177386157561</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-2.865445792273189</v>
+        <v>0.0723910090060037</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6244</v>
+        <v>6176</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>433.7175698652848</v>
+        <v>498.9745634687181</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>28.7</v>
+        <v>101</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>47.36093285092731</v>
+        <v>47.08376093490611</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>22.79102509455966</v>
+        <v>31.58395371175888</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.8717569865284822</v>
+        <v>1.897456346871812</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0105580424258247</v>
+        <v>-0.5554101584944313</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6218</v>
+        <v>6168</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>431.6937743354158</v>
+        <v>498.4556125765584</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>36.8</v>
+        <v>26.05</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>46.12823947710904</v>
+        <v>44.90223512376239</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>11.63592046235071</v>
+        <v>19.27086728741284</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.1693774335415784</v>
+        <v>0.3455612576558354</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.7173853464381907</v>
+        <v>-0.2681468591200714</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6464</v>
+        <v>6177</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>423.828630138682</v>
+        <v>489.6930920671222</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>78</v>
+        <v>45.45</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>62.04995185785521</v>
+        <v>55.63091747517184</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>16.94276279590703</v>
+        <v>15.59989183891075</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.3828630138682005</v>
+        <v>0.9693092067122188</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.0136086352052432</v>
+        <v>0.2259454522819315</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6176</v>
+        <v>6229</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>408.9745634687181</v>
+        <v>480.6866068603246</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>101</v>
+        <v>26.95</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,16 +5004,16 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>47.08376076827592</v>
+        <v>51.28243736204278</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>31.58395326196477</v>
+        <v>17.53812766144004</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.897456346871812</v>
+        <v>0.5686606860324639</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.5554101586852183</v>
+        <v>-0.1544276018977238</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6235</v>
+        <v>6443</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>400.738076201092</v>
+        <v>459.5955932505867</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>44.15</v>
+        <v>39.9</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>52.00990515120389</v>
+        <v>47.15524747000665</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>28.44053366562022</v>
+        <v>25.07885397532246</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.5738076201092051</v>
+        <v>0.4595593250586646</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.5834166025214427</v>
+        <v>0.0036627845221793</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6222</v>
+        <v>6201</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>397.0398338354336</v>
+        <v>456.9464761080391</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>20.4</v>
+        <v>49</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>40.95450996706313</v>
+        <v>49.82552447512506</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>33.65149652359051</v>
+        <v>28.5950528067837</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.2039833835433551</v>
+        <v>0.6946476108039101</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.0934735610932564</v>
+        <v>0.2483548225340742</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6462</v>
+        <v>6217</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>393.6534488355433</v>
+        <v>449.6564222831479</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>116</v>
+        <v>254</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>39.35789721312553</v>
+        <v>44.42894616275048</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>26.91089234921579</v>
+        <v>20.11984100863028</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.3653448835543321</v>
+        <v>1.465642228314788</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-3.163624894354971</v>
+        <v>-4.499822026718908</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6275</v>
+        <v>6266</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>387.9579997621631</v>
+        <v>447.2545617194276</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>50.1</v>
+        <v>28.05</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>50.27963206474274</v>
+        <v>55.95384808322956</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>21.70422462232361</v>
+        <v>21.84613782869669</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.7957999762163083</v>
+        <v>0.7254561719427558</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.4073094425026133</v>
+        <v>0.1423716542668616</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6246</v>
+        <v>6426</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>386.0601594060487</v>
+        <v>439.5259073609012</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>16.1</v>
+        <v>229.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>53.25126921265147</v>
+        <v>42.9394813749141</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>17.75359768418786</v>
+        <v>23.33927277300355</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.10601594060487</v>
+        <v>0.4525907360901153</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.07164441697451721</v>
+        <v>-6.654948736424631</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6442</v>
+        <v>6244</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>367.2699743492909</v>
+        <v>433.7175698652848</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>2055</v>
+        <v>28.7</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>53.44541088177046</v>
+        <v>47.36093284463624</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>15.20186751730326</v>
+        <v>22.79102516261724</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.22699743492909</v>
+        <v>0.8717569865284822</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>23.75254587108215</v>
+        <v>-0.0105580422254907</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6229</v>
+        <v>6218</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>365.6866068603246</v>
+        <v>431.6937743354158</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>26.95</v>
+        <v>36.8</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>51.28243746787025</v>
+        <v>46.128239542316</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>17.5381275034261</v>
+        <v>11.63592046235071</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5686606860324639</v>
+        <v>0.1693774335415784</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.1544276022793131</v>
+        <v>-0.7173853464381907</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6185</v>
+        <v>6216</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>361.6321773861576</v>
+        <v>426.1044778741462</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>14.35</v>
+        <v>23.6</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>56.14113380087285</v>
+        <v>53.71271856018161</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>19.15640886836333</v>
+        <v>26.02797099742386</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6632177386157561</v>
+        <v>1.11044778741462</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0723910090060037</v>
+        <v>0.2505966029476367</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6202</v>
+        <v>6464</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>346.2703715416324</v>
+        <v>423.828630138682</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>44.71418157425173</v>
+        <v>62.04995141179337</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>16.7798015564972</v>
+        <v>16.94276291629354</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.6270371541632355</v>
+        <v>0.3828630138682005</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.4215476328164615</v>
+        <v>-0.0136086350335254</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6201</v>
+        <v>6230</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>341.9464761080391</v>
+        <v>414.4496421949283</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>49</v>
+        <v>139</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>49.825524256972</v>
+        <v>45.1725822650918</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>28.59505272629521</v>
+        <v>12.41733236009211</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.6946476108039101</v>
+        <v>0.4449642194928336</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.2483548224959176</v>
+        <v>1.031651963568034</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6243</v>
+        <v>6235</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>331.729586861577</v>
+        <v>400.738076201092</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>32.5</v>
+        <v>44.15</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>43.16408734056839</v>
+        <v>52.00990527941354</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>26.02364641293025</v>
+        <v>28.44053375551221</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.172958686157702</v>
+        <v>0.5738076201092051</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.2686465906397011</v>
+        <v>0.5834166026645425</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6230</v>
+        <v>6222</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>299.4496421949283</v>
+        <v>397.0398338354336</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>139</v>
+        <v>20.4</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>45.17258205473532</v>
+        <v>40.95451012922869</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>12.41733246476184</v>
+        <v>33.6514963851679</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.4449642194928336</v>
+        <v>0.2039833835433551</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>1.031651963949604</v>
+        <v>-0.0934735610932564</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6210</v>
+        <v>6462</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>295.7570077862636</v>
+        <v>393.6534488355433</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>21.05</v>
+        <v>116</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>52.21973799085917</v>
+        <v>39.35789722206243</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>19.171607514265</v>
+        <v>26.91089234266146</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5757007786263636</v>
+        <v>0.3653448835543321</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,11 +5711,11 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0705842604729179</v>
+        <v>-3.163624893629931</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5732,7 @@
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>291.6308466099608</v>
+        <v>381.6308466099608</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>23.6</v>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>46.43492779279734</v>
+        <v>46.4349278685149</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>19.87127198901124</v>
+        <v>19.87127199042612</v>
       </c>
       <c r="J100" s="2" t="n">
         <v>0.1630846609960785</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.6825386604936167</v>
+        <v>-0.6825386606557942</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6438</v>
+        <v>6187</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>289.182867601568</v>
+        <v>377.6818940640218</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>157.5</v>
+        <v>1120</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,49 +5799,49 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>35.90650377414495</v>
+        <v>50.39676479141047</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>15.73149067089146</v>
+        <v>16.38449674885142</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.9182867601567952</v>
+        <v>1.268189406402181</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M101" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-1.168646834310076</v>
+        <v>-11.48527127602241</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6216</v>
+        <v>6202</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>286.1044778741462</v>
+        <v>346.2703715416324</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>23.6</v>
+        <v>55</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>53.71271843723117</v>
+        <v>44.71418156650565</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>26.02797080688828</v>
+        <v>16.77980165660381</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.11044778741462</v>
+        <v>0.6270371541632355</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.2505966028999392</v>
+        <v>-0.4215476324253329</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6441</v>
+        <v>6184</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>285.1732333008591</v>
+        <v>332.6000404420438</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>24.05</v>
+        <v>47</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>46.6404672936832</v>
+        <v>60.83306196072419</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>18.12708098381633</v>
+        <v>18.16621006154823</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.5173233300859128</v>
+        <v>0.7600040442043794</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.1806400553619172</v>
+        <v>0.1482970427649213</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6187</v>
+        <v>6243</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>萬潤</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>282.6818940640218</v>
+        <v>331.729586861577</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>1120</v>
+        <v>32.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>50.39676478201574</v>
+        <v>43.16408742408546</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>16.38449679038335</v>
+        <v>26.02364643082682</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.268189406402181</v>
+        <v>1.172958686157702</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-11.48527127649951</v>
+        <v>-0.2686465905156813</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6472</v>
+        <v>6167</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>267.2897521814568</v>
+        <v>311.2466820021796</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>371.5</v>
+        <v>12</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>47.42763410495104</v>
+        <v>48.05840996324805</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>26.42912490804517</v>
+        <v>17.77465546395974</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.7289752181456796</v>
+        <v>0.6246682002179557</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>2.397758300163108</v>
+        <v>0.1111412562657949</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6423</v>
+        <v>6210</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>236.1130819962518</v>
+        <v>295.7570077862636</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>90.2</v>
+        <v>21.05</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,16 +6064,16 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>36.531643977114</v>
+        <v>52.21973789930632</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>17.76697872757082</v>
+        <v>19.1716074556367</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.6113081996251798</v>
+        <v>0.5757007786263636</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-1.42521955708776</v>
+        <v>-0.0705842603298229</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6177</v>
+        <v>6276</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>229.6930920671222</v>
+        <v>291.8589175099869</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>45.45</v>
+        <v>27.95</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>55.63091744036856</v>
+        <v>44.02764431834176</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15.59989181152982</v>
+        <v>16.26704191027493</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.9693092067122188</v>
+        <v>1.185891750998697</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.2259454521388262</v>
+        <v>0.09821921399546241</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6188</v>
+        <v>6438</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>227.9977540336292</v>
+        <v>289.182867601568</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>84.09999999999999</v>
+        <v>157.5</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>46.81196259995227</v>
+        <v>35.90650407587786</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>11.51328092513419</v>
+        <v>15.73149068557267</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.799775403362923</v>
+        <v>0.9182867601567952</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.3572594759592831</v>
+        <v>-1.168646834500866</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6233</v>
+        <v>6228</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>227.5535530285866</v>
+        <v>287.6111819515103</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>24.7</v>
+        <v>20.85</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>42.19017339948277</v>
+        <v>48.56854817193508</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>9.436086379600679</v>
+        <v>2.858966188574583</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.755355302858663</v>
+        <v>0.2611181951510351</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.0479760246778199</v>
+        <v>-0.0275580518926706</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6184</v>
+        <v>6441</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>217.6000404420438</v>
+        <v>285.1732333008591</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>47</v>
+        <v>24.05</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>60.83306179357803</v>
+        <v>46.64046738380864</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>18.16620998635788</v>
+        <v>18.12708100432849</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.7600040442043794</v>
+        <v>0.5173233300859128</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.1482970427649213</v>
+        <v>-0.180640055438237</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6431</v>
+        <v>6423</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>光麗-KY</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>178.8528554839755</v>
+        <v>236.1130819962518</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>18.5</v>
+        <v>90.2</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>34.98824490403521</v>
+        <v>36.5316439529055</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>17.32395816103323</v>
+        <v>17.76697877482334</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.8852855483975504</v>
+        <v>0.6113081996251798</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.1755268344590881</v>
+        <v>-1.42521955685881</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6276</v>
+        <v>6188</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>176.858917509987</v>
+        <v>227.9977540336292</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>27.95</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>44.02764455849573</v>
+        <v>46.81196262125246</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>16.26704160376266</v>
+        <v>11.51328089840732</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.185891750998697</v>
+        <v>0.799775403362923</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.0982192133467608</v>
+        <v>0.3572594763027098</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6228</v>
+        <v>6233</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>172.6111819515104</v>
+        <v>227.5535530285866</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>20.85</v>
+        <v>24.7</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>48.56854815862921</v>
+        <v>42.19017349826324</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>2.858966042159801</v>
+        <v>9.43608625040592</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.2611181951510351</v>
+        <v>1.755355302858663</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.0275580526844663</v>
+        <v>-0.0479760246110422</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6198</v>
+        <v>6431</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>光麗-KY</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>171.5395399222583</v>
+        <v>178.8528554839755</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>20.65</v>
+        <v>18.5</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>50.65889498644358</v>
+        <v>34.98824486212682</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>9.20086300485805</v>
+        <v>17.32395811979791</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.1539539922258331</v>
+        <v>0.8852855483975504</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.1202773321771452</v>
+        <v>-0.175526834220596</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6167</v>
+        <v>6241</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>171.2466820021796</v>
+        <v>174.0213041792685</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>12</v>
+        <v>10.45</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>48.0584099375936</v>
+        <v>52.91111160717111</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>17.77465544509321</v>
+        <v>15.83518723641249</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.6246682002179557</v>
+        <v>0.402130417926846</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.1111412562494458</v>
+        <v>0.0381408511273027</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6477</v>
+        <v>6198</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>168.5094954244715</v>
+        <v>171.5395399222583</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>33.7</v>
+        <v>20.65</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>46.87873136781116</v>
+        <v>50.65889503052438</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>18.6322416885832</v>
+        <v>9.200863004858048</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.8509495424471546</v>
+        <v>0.1539539922258331</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,11 +6612,11 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.0183866558111254</v>
+        <v>0.1202773321294489</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6633,7 @@
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>108.8193640139415</v>
+        <v>168.8193640139415</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>8.890000000000001</v>
@@ -6647,7 +6647,7 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>46.98318148563839</v>
+        <v>50.55900061937332</v>
       </c>
       <c r="I117" s="2" t="n">
         <v>2.395858819217372</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.0037734185591829</v>
+        <v>-0.0135600057931723</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, obv_uptrend</t>
+          <t>above_ema60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6236</v>
+        <v>6477</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>安集</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>105</v>
+        <v>168.5094954244715</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>0</v>
+        <v>33.7</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>47.91910848085592</v>
+        <v>46.87873142716629</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>10.01177896761618</v>
+        <v>18.63224161683732</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0</v>
+        <v>0.8509495424471546</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0521576713719164</v>
+        <v>0.0183866559256046</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>6183</v>
+        <v>6236</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>中湛</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>102.6226007748499</v>
+        <v>105</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>90.2</v>
+        <v>0</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>35.60557180572017</v>
+        <v>47.91910848085592</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>19.52551289211051</v>
+        <v>10.01177890581492</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.262260077484991</v>
+        <v>0</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0494416258954695</v>
+        <v>-0.0521576713719164</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6241</v>
+        <v>6183</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>鑫永洋</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>34.02130417926846</v>
+        <v>102.6226007748499</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>10.45</v>
+        <v>90.2</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>52.91111151380024</v>
+        <v>35.60557221417521</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>15.8351872204817</v>
+        <v>19.52551304413245</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.402130417926846</v>
+        <v>1.262260077484991</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,11 +6824,11 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.0381408510509872</v>
+        <v>-0.0494416261053478</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
